--- a/SAM_QIP_Team_Workbook.xlsx
+++ b/SAM_QIP_Team_Workbook.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">YOUR PITCH &amp; FIRST CHANGE  (Stages 1–2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Draft it at aimqa.github.io/SAMQIP — Pitch and 2×2 tabs — then paste the final wording here.</t>
+    <t xml:space="preserve">Draft it at aimqa.github.io/SAM-QI-diagram-tool — Pitch and 2×2 tabs — then paste the final wording here.</t>
   </si>
   <si>
     <t xml:space="preserve">1  The problem</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">AT A GLANCE  (updates itself)</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw your process map &amp; driver diagram  →  aimqa.github.io/SAMQIP</t>
+    <t xml:space="preserve">Draw your process map &amp; driver diagram  →  aimqa.github.io/SAM-QI-diagram-tool</t>
   </si>
   <si>
     <t xml:space="preserve">SAM QIP Diagram Tool — WHO quality lens built in · worked VTE example · export the PNG straight into your slides</t>
@@ -177,7 +177,7 @@
     <t xml:space="preserve">–  New team member? Read the SAM QIP Roadmap deck first — this workbook follows its seven stages.</t>
   </si>
   <si>
-    <t xml:space="preserve">–  Draw it in the tool, track it here: process maps, 5 Whys, driver diagrams and the 2×2 are built at aimqa.github.io/SAMQIP; this workbook holds the decisions, the data and the write-up. Paste the tool’s PNGs into your slides.</t>
+    <t xml:space="preserve">–  Draw it in the tool, track it here: process maps, 5 Whys, driver diagrams and the 2×2 are built at aimqa.github.io/SAM-QI-diagram-tool; this workbook holds the decisions, the data and the write-up. Paste the tool’s PNGs into your slides.</t>
   </si>
   <si>
     <t xml:space="preserve">–  WHO quality lens — quality services are effective · safe · people-centred · timely · equitable · integrated · efficient. Your aim should target at least one.</t>
@@ -366,7 +366,7 @@
     <t xml:space="preserve">A long wait next to a short task is usually where the delay lives — and often the easiest thing to fix.</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw it as a picture  →  aimqa.github.io/SAMQIP  —  the Process Map tab turns these steps into a diagram you can paste into your slides.</t>
+    <t xml:space="preserve">Draw it as a picture  →  aimqa.github.io/SAM-QI-diagram-tool  —  the Process Map tab turns these steps into a diagram you can paste into your slides.</t>
   </si>
   <si>
     <t xml:space="preserve">Causes — what is driving the problem</t>
@@ -423,7 +423,7 @@
     <t xml:space="preserve">If everything is a hunch, you are guessing. Go and check two or three before you pick one to change.</t>
   </si>
   <si>
-    <t xml:space="preserve">Draw the fishbone  →  aimqa.github.io/SAMQIP  —  the Fishbone tab turns these causes straight into a driver diagram.</t>
+    <t xml:space="preserve">Draw the fishbone  →  aimqa.github.io/SAM-QI-diagram-tool  —  the Fishbone tab turns these causes straight into a driver diagram.</t>
   </si>
   <si>
     <t xml:space="preserve">Data Plan — one outcome, one process, one balancing measure</t>
@@ -474,7 +474,7 @@
     <t xml:space="preserve">Balancing</t>
   </si>
   <si>
-    <t xml:space="preserve">Need the diagrams first?  Draw your process map &amp; driver diagram at  aimqa.github.io/SAMQIP  — then paste the PNGs into your slides.</t>
+    <t xml:space="preserve">Need the diagrams first?  Draw your process map &amp; driver diagram at  aimqa.github.io/SAM-QI-diagram-tool  — then paste the PNGs into your slides.</t>
   </si>
   <si>
     <t xml:space="preserve">Data Log — feeds the run chart automatically</t>
@@ -742,7 +742,7 @@
     <t xml:space="preserve">Attached?</t>
   </si>
   <si>
-    <t xml:space="preserve">From aimqa.github.io/SAMQIP — Download PNG</t>
+    <t xml:space="preserve">From aimqa.github.io/SAM-QI-diagram-tool — Download PNG</t>
   </si>
   <si>
     <t xml:space="preserve">Driver diagram (PNG)</t>
